--- a/invitados.xlsx
+++ b/invitados.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\green\Downloads\boda brian kelly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian.fernandez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0FC27DB-3CA8-47CE-ABDB-81E1B3B06920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA0F981-FA9F-4801-8BCF-368EEAE1B411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D3C44EFB-CC1C-46B2-8964-FA404AFB8647}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D3C44EFB-CC1C-46B2-8964-FA404AFB8647}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>codigo</t>
   </si>
@@ -56,52 +56,67 @@
     <t>familia Gomez</t>
   </si>
   <si>
-    <t>juan Gomez</t>
-  </si>
-  <si>
     <t>Miranda Fernandez</t>
   </si>
   <si>
-    <t>silvana</t>
-  </si>
-  <si>
-    <t>jose</t>
-  </si>
-  <si>
-    <t>geiler</t>
-  </si>
-  <si>
-    <t>mami abuela</t>
-  </si>
-  <si>
-    <t>maye</t>
-  </si>
-  <si>
-    <t>la mona</t>
-  </si>
-  <si>
-    <t>jose david</t>
-  </si>
-  <si>
-    <t>kata</t>
-  </si>
-  <si>
-    <t>carlos mario</t>
-  </si>
-  <si>
-    <t>hector</t>
-  </si>
-  <si>
-    <t>nefer</t>
-  </si>
-  <si>
-    <t>jonatan</t>
-  </si>
-  <si>
-    <t>luis tania</t>
-  </si>
-  <si>
-    <t>Geo y Sevas</t>
+    <t>Osiris</t>
+  </si>
+  <si>
+    <t>Narcides</t>
+  </si>
+  <si>
+    <t>Yosana</t>
+  </si>
+  <si>
+    <t>Brayan Cardenas</t>
+  </si>
+  <si>
+    <t>Juan Gomez</t>
+  </si>
+  <si>
+    <t>Silvana</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>Geiler</t>
+  </si>
+  <si>
+    <t>Nora Cantillo</t>
+  </si>
+  <si>
+    <t>Mayerlis</t>
+  </si>
+  <si>
+    <t>Yanileth</t>
+  </si>
+  <si>
+    <t>Jose David</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katerine </t>
+  </si>
+  <si>
+    <t>Carlos M y Leonor</t>
+  </si>
+  <si>
+    <t>Hector Durango</t>
+  </si>
+  <si>
+    <t>Nefer</t>
+  </si>
+  <si>
+    <t>Jonathan</t>
+  </si>
+  <si>
+    <t>Luis &amp; Tania</t>
+  </si>
+  <si>
+    <t>Geovanis</t>
+  </si>
+  <si>
+    <t>Luis &amp; Tatiana</t>
   </si>
 </sst>
 </file>
@@ -180,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -192,6 +207,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -528,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4355357-D613-4929-9CAB-FC2F66DF68B3}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
@@ -553,7 +574,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -572,7 +593,7 @@
         <v>103</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -583,7 +604,7 @@
         <v>104</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3">
         <v>3</v>
@@ -594,7 +615,7 @@
         <v>105</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -605,7 +626,7 @@
         <v>106</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3">
         <v>1</v>
@@ -616,7 +637,7 @@
         <v>107</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3">
         <v>2</v>
@@ -627,7 +648,7 @@
         <v>108</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3">
         <v>1</v>
@@ -638,7 +659,7 @@
         <v>109</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3">
         <v>3</v>
@@ -649,7 +670,7 @@
         <v>110</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3">
         <v>2</v>
@@ -660,7 +681,7 @@
         <v>111</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3">
         <v>2</v>
@@ -671,7 +692,7 @@
         <v>112</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3">
         <v>2</v>
@@ -682,7 +703,7 @@
         <v>113</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C14" s="3">
         <v>2</v>
@@ -693,7 +714,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3">
         <v>2</v>
@@ -704,7 +725,7 @@
         <v>115</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C16" s="3">
         <v>2</v>
@@ -715,7 +736,7 @@
         <v>116</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C17" s="3">
         <v>2</v>
@@ -726,7 +747,7 @@
         <v>117</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C18" s="3">
         <v>2</v>
@@ -737,9 +758,64 @@
         <v>118</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C19" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>119</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>120</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>121</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>122</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>123</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="6">
         <v>2</v>
       </c>
     </row>

--- a/invitados.xlsx
+++ b/invitados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian.fernandez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA0F981-FA9F-4801-8BCF-368EEAE1B411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE016F6-64C2-4037-ACE9-80F5E4F51A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D3C44EFB-CC1C-46B2-8964-FA404AFB8647}"/>
   </bookViews>
@@ -50,15 +50,6 @@
     <t>cupos</t>
   </si>
   <si>
-    <t>familia contreras Cardenas</t>
-  </si>
-  <si>
-    <t>familia Gomez</t>
-  </si>
-  <si>
-    <t>Miranda Fernandez</t>
-  </si>
-  <si>
     <t>Osiris</t>
   </si>
   <si>
@@ -101,9 +92,6 @@
     <t>Carlos M y Leonor</t>
   </si>
   <si>
-    <t>Hector Durango</t>
-  </si>
-  <si>
     <t>Nefer</t>
   </si>
   <si>
@@ -117,6 +105,18 @@
   </si>
   <si>
     <t>Luis &amp; Tatiana</t>
+  </si>
+  <si>
+    <t>Hector Duran</t>
+  </si>
+  <si>
+    <t>Familia contreras Cardenas</t>
+  </si>
+  <si>
+    <t>Familia Gomez</t>
+  </si>
+  <si>
+    <t>Familia Miranda Fernandez</t>
   </si>
 </sst>
 </file>
@@ -552,7 +552,7 @@
   <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -571,7 +571,7 @@
         <v>101</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3">
         <v>3</v>
@@ -582,7 +582,7 @@
         <v>102</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3">
         <v>4</v>
@@ -593,7 +593,7 @@
         <v>103</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -604,7 +604,7 @@
         <v>104</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3">
         <v>3</v>
@@ -615,7 +615,7 @@
         <v>105</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -626,7 +626,7 @@
         <v>106</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C7" s="3">
         <v>1</v>
@@ -637,7 +637,7 @@
         <v>107</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3">
         <v>2</v>
@@ -648,7 +648,7 @@
         <v>108</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3">
         <v>1</v>
@@ -659,7 +659,7 @@
         <v>109</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3">
         <v>3</v>
@@ -670,7 +670,7 @@
         <v>110</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3">
         <v>2</v>
@@ -681,7 +681,7 @@
         <v>111</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3">
         <v>2</v>
@@ -692,7 +692,7 @@
         <v>112</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3">
         <v>2</v>
@@ -703,7 +703,7 @@
         <v>113</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3">
         <v>2</v>
@@ -714,7 +714,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3">
         <v>2</v>
@@ -725,7 +725,7 @@
         <v>115</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C16" s="3">
         <v>2</v>
@@ -736,7 +736,7 @@
         <v>116</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C17" s="3">
         <v>2</v>
@@ -747,7 +747,7 @@
         <v>117</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C18" s="3">
         <v>2</v>
@@ -758,7 +758,7 @@
         <v>118</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C19" s="4">
         <v>2</v>
@@ -769,7 +769,7 @@
         <v>119</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C20" s="6">
         <v>1</v>
@@ -780,7 +780,7 @@
         <v>120</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C21" s="6">
         <v>1</v>
@@ -791,10 +791,10 @@
         <v>121</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C22" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -802,7 +802,7 @@
         <v>122</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C23" s="6">
         <v>1</v>
@@ -813,7 +813,7 @@
         <v>123</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C24" s="6">
         <v>2</v>

--- a/invitados.xlsx
+++ b/invitados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian.fernandez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE016F6-64C2-4037-ACE9-80F5E4F51A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909AE134-E957-40CD-8773-52AF85E8E346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D3C44EFB-CC1C-46B2-8964-FA404AFB8647}"/>
   </bookViews>
@@ -110,13 +110,13 @@
     <t>Hector Duran</t>
   </si>
   <si>
-    <t>Familia contreras Cardenas</t>
-  </si>
-  <si>
-    <t>Familia Gomez</t>
-  </si>
-  <si>
-    <t>Familia Miranda Fernandez</t>
+    <t>Familia Contreras Cardenas</t>
+  </si>
+  <si>
+    <t>Familia Gomez Hernández</t>
+  </si>
+  <si>
+    <t>Familia Miranda Fernández</t>
   </si>
 </sst>
 </file>

--- a/invitados.xlsx
+++ b/invitados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian.fernandez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909AE134-E957-40CD-8773-52AF85E8E346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6DAA1B-7E56-4016-A679-BA34929D4FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D3C44EFB-CC1C-46B2-8964-FA404AFB8647}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D3C44EFB-CC1C-46B2-8964-FA404AFB8647}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>codigo</t>
   </si>
@@ -89,9 +89,6 @@
     <t xml:space="preserve">Katerine </t>
   </si>
   <si>
-    <t>Carlos M y Leonor</t>
-  </si>
-  <si>
     <t>Nefer</t>
   </si>
   <si>
@@ -117,6 +114,18 @@
   </si>
   <si>
     <t>Familia Miranda Fernández</t>
+  </si>
+  <si>
+    <t>Ellery Ricaurte</t>
+  </si>
+  <si>
+    <t>Hugo &amp; Xiomara</t>
+  </si>
+  <si>
+    <t>Carlos M  &amp; Leonor</t>
+  </si>
+  <si>
+    <t>Estefania Fernandez</t>
   </si>
 </sst>
 </file>
@@ -549,10 +558,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4355357-D613-4929-9CAB-FC2F66DF68B3}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -571,7 +580,7 @@
         <v>101</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3">
         <v>3</v>
@@ -582,7 +591,7 @@
         <v>102</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3">
         <v>4</v>
@@ -604,10 +613,10 @@
         <v>104</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -703,7 +712,7 @@
         <v>113</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3">
         <v>2</v>
@@ -714,7 +723,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="3">
         <v>2</v>
@@ -725,7 +734,7 @@
         <v>115</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="3">
         <v>2</v>
@@ -736,7 +745,7 @@
         <v>116</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="3">
         <v>2</v>
@@ -747,7 +756,7 @@
         <v>117</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18" s="3">
         <v>2</v>
@@ -758,7 +767,7 @@
         <v>118</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19" s="4">
         <v>2</v>
@@ -813,10 +822,43 @@
         <v>123</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" s="6">
         <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>124</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>125</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>126</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/invitados.xlsx
+++ b/invitados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian.fernandez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6DAA1B-7E56-4016-A679-BA34929D4FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FAA616D-298D-44F7-AC7B-A54C58E10A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D3C44EFB-CC1C-46B2-8964-FA404AFB8647}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D3C44EFB-CC1C-46B2-8964-FA404AFB8647}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -92,9 +92,6 @@
     <t>Nefer</t>
   </si>
   <si>
-    <t>Jonathan</t>
-  </si>
-  <si>
     <t>Luis &amp; Tania</t>
   </si>
   <si>
@@ -126,6 +123,9 @@
   </si>
   <si>
     <t>Estefania Fernandez</t>
+  </si>
+  <si>
+    <t>Jonathan Moreno</t>
   </si>
 </sst>
 </file>
@@ -580,7 +580,7 @@
         <v>101</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3">
         <v>3</v>
@@ -591,7 +591,7 @@
         <v>102</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3">
         <v>4</v>
@@ -613,7 +613,7 @@
         <v>104</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3">
         <v>2</v>
@@ -712,7 +712,7 @@
         <v>113</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="3">
         <v>2</v>
@@ -723,7 +723,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3">
         <v>2</v>
@@ -745,7 +745,7 @@
         <v>116</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C17" s="3">
         <v>2</v>
@@ -756,7 +756,7 @@
         <v>117</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" s="3">
         <v>2</v>
@@ -767,7 +767,7 @@
         <v>118</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19" s="4">
         <v>2</v>
@@ -822,7 +822,7 @@
         <v>123</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C24" s="6">
         <v>2</v>
@@ -833,7 +833,7 @@
         <v>124</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="6">
         <v>2</v>
@@ -844,7 +844,7 @@
         <v>125</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="6">
         <v>2</v>
@@ -855,7 +855,7 @@
         <v>126</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="6">
         <v>1</v>

--- a/invitados.xlsx
+++ b/invitados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian.fernandez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FAA616D-298D-44F7-AC7B-A54C58E10A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FC9377-6827-4320-895D-8E04A7E6DECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D3C44EFB-CC1C-46B2-8964-FA404AFB8647}"/>
   </bookViews>
@@ -71,9 +71,6 @@
     <t>Jose</t>
   </si>
   <si>
-    <t>Geiler</t>
-  </si>
-  <si>
     <t>Nora Cantillo</t>
   </si>
   <si>
@@ -126,6 +123,9 @@
   </si>
   <si>
     <t>Jonathan Moreno</t>
+  </si>
+  <si>
+    <t>Geiler &amp; Andrea</t>
   </si>
 </sst>
 </file>
@@ -580,7 +580,7 @@
         <v>101</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3">
         <v>3</v>
@@ -591,7 +591,7 @@
         <v>102</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3">
         <v>4</v>
@@ -613,7 +613,7 @@
         <v>104</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3">
         <v>2</v>
@@ -646,7 +646,7 @@
         <v>107</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C8" s="3">
         <v>2</v>
@@ -657,7 +657,7 @@
         <v>108</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="3">
         <v>1</v>
@@ -668,7 +668,7 @@
         <v>109</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3">
         <v>3</v>
@@ -679,7 +679,7 @@
         <v>110</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3">
         <v>2</v>
@@ -690,7 +690,7 @@
         <v>111</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3">
         <v>2</v>
@@ -701,7 +701,7 @@
         <v>112</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3">
         <v>2</v>
@@ -712,7 +712,7 @@
         <v>113</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="3">
         <v>2</v>
@@ -723,7 +723,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="3">
         <v>2</v>
@@ -734,7 +734,7 @@
         <v>115</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" s="3">
         <v>2</v>
@@ -745,7 +745,7 @@
         <v>116</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="3">
         <v>2</v>
@@ -756,7 +756,7 @@
         <v>117</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" s="3">
         <v>2</v>
@@ -767,7 +767,7 @@
         <v>118</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" s="4">
         <v>2</v>
@@ -822,7 +822,7 @@
         <v>123</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C24" s="6">
         <v>2</v>
@@ -833,7 +833,7 @@
         <v>124</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="6">
         <v>2</v>
@@ -844,7 +844,7 @@
         <v>125</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26" s="6">
         <v>2</v>
@@ -855,7 +855,7 @@
         <v>126</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" s="6">
         <v>1</v>

--- a/invitados.xlsx
+++ b/invitados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian.fernandez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FC9377-6827-4320-895D-8E04A7E6DECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF689FBD-4277-46C2-AB32-23564374DB1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D3C44EFB-CC1C-46B2-8964-FA404AFB8647}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>codigo</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>Geiler &amp; Andrea</t>
+  </si>
+  <si>
+    <t>Monica &amp; Emiro</t>
   </si>
 </sst>
 </file>
@@ -558,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4355357-D613-4929-9CAB-FC2F66DF68B3}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
@@ -861,6 +864,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>127</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="6">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/invitados.xlsx
+++ b/invitados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian.fernandez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF689FBD-4277-46C2-AB32-23564374DB1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36709065-CA30-46EE-9822-3C1FD36FF880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D3C44EFB-CC1C-46B2-8964-FA404AFB8647}"/>
   </bookViews>
@@ -98,9 +98,6 @@
     <t>Luis &amp; Tatiana</t>
   </si>
   <si>
-    <t>Hector Duran</t>
-  </si>
-  <si>
     <t>Familia Contreras Cardenas</t>
   </si>
   <si>
@@ -129,6 +126,9 @@
   </si>
   <si>
     <t>Monica &amp; Emiro</t>
+  </si>
+  <si>
+    <t>Hector &amp; Ana</t>
   </si>
 </sst>
 </file>
@@ -583,7 +583,7 @@
         <v>101</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3">
         <v>3</v>
@@ -594,7 +594,7 @@
         <v>102</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3">
         <v>4</v>
@@ -616,7 +616,7 @@
         <v>104</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3">
         <v>2</v>
@@ -649,7 +649,7 @@
         <v>107</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3">
         <v>2</v>
@@ -715,7 +715,7 @@
         <v>113</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="3">
         <v>2</v>
@@ -726,7 +726,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3">
         <v>2</v>
@@ -748,7 +748,7 @@
         <v>116</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17" s="3">
         <v>2</v>
@@ -836,7 +836,7 @@
         <v>124</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" s="6">
         <v>2</v>
@@ -847,7 +847,7 @@
         <v>125</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C26" s="6">
         <v>2</v>
@@ -858,7 +858,7 @@
         <v>126</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" s="6">
         <v>1</v>
@@ -869,7 +869,7 @@
         <v>127</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C28" s="6">
         <v>2</v>
